--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU14"/>
+  <dimension ref="A1:AU16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46219.8125</v>
+        <v>46219.77083333334</v>
       </c>
     </row>
     <row r="8">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>46219.83333333334</v>
+        <v>46219.8125</v>
       </c>
     </row>
     <row r="10">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>46219.85416666666</v>
+        <v>46219.83333333334</v>
       </c>
     </row>
     <row r="12">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="O12" t="n">
-        <v>5.41</v>
+        <v>3.97</v>
       </c>
       <c r="P12" t="n">
-        <v>7.6</v>
+        <v>4.04</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>46219.89583333334</v>
+        <v>46219.85416666666</v>
       </c>
     </row>
     <row r="13">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2519,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46219.89583333334</v>
+        <v>46219.875</v>
       </c>
     </row>
     <row r="14">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>5.08</v>
+        <v>5.41</v>
       </c>
       <c r="P14" t="n">
-        <v>6.91</v>
+        <v>7.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2736,6 +2736,324 @@
         <v>0</v>
       </c>
       <c r="AU14" s="3" t="n">
+        <v>46219.89583333334</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="3" t="n">
+        <v>46219.89583333334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="3" t="n">
         <v>46219.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P9" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P8" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>5.41</v>
+        <v>3.83</v>
       </c>
       <c r="P14" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>5.41</v>
+        <v>3.83</v>
       </c>
       <c r="P15" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P9" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>5.41</v>
+        <v>3.83</v>
       </c>
       <c r="P14" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P8" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>5.41</v>
+        <v>3.83</v>
       </c>
       <c r="P15" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P9" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>5.41</v>
+        <v>3.83</v>
       </c>
       <c r="P14" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P8" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>5.41</v>
+        <v>3.83</v>
       </c>
       <c r="P15" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P9" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>5.41</v>
+        <v>3.83</v>
       </c>
       <c r="P14" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P8" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P9" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P8" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>5.41</v>
+        <v>3.83</v>
       </c>
       <c r="P15" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>5.41</v>
+        <v>3.83</v>
       </c>
       <c r="P14" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>5.41</v>
+        <v>3.83</v>
       </c>
       <c r="P15" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>5.41</v>
+        <v>3.83</v>
       </c>
       <c r="P14" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P9" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>5.41</v>
+        <v>3.83</v>
       </c>
       <c r="P15" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P8" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>5.41</v>
+        <v>3.83</v>
       </c>
       <c r="P14" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG8" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P9" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2324,34 +2324,34 @@
         <v>4.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA12" t="n">
         <v>1.58</v>
@@ -2360,19 +2360,19 @@
         <v>2.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2642,40 +2642,40 @@
         <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AC14" t="n">
         <v>2.15</v>
@@ -2684,13 +2684,13 @@
         <v>1.61</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2801,40 +2801,40 @@
         <v>7.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AC15" t="n">
         <v>1.95</v>
@@ -2843,13 +2843,13 @@
         <v>1.73</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2960,40 +2960,40 @@
         <v>6.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC16" t="n">
         <v>1.95</v>
@@ -3002,13 +3002,13 @@
         <v>1.73</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P8" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T8" t="n">
-        <v>3.11</v>
+        <v>2.69</v>
       </c>
       <c r="U8" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.05</v>
+        <v>2.38</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>2.69</v>
+        <v>3.11</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="S14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="U14" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.51</v>
+        <v>2.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.4</v>
+        <v>2.88</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="P15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2.88</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="P14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.88</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T15" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="U15" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.51</v>
+        <v>2.76</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.4</v>
+        <v>2.88</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
         <v>2.63</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.05</v>
+        <v>2.38</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>2.69</v>
+        <v>3.11</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG8" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P9" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T9" t="n">
-        <v>3.11</v>
+        <v>2.69</v>
       </c>
       <c r="U9" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.83</v>
+        <v>5.41</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="S14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="U14" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.51</v>
+        <v>2.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.4</v>
+        <v>2.88</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="P15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2.88</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
         <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="R7" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
         <v>2.63</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
         <v>3.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
         <v>1.38</v>
@@ -1682,28 +1682,28 @@
         <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>3.99</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="R8" t="n">
         <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T8" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="U8" t="n">
         <v>2.62</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
         <v>1.06</v>
@@ -1715,13 +1715,13 @@
         <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC8" t="n">
         <v>3.1</v>
@@ -1733,7 +1733,7 @@
         <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AG8" t="n">
         <v>2.05</v>
@@ -1752,7 +1752,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1865,13 +1865,13 @@
         <v>1.38</v>
       </c>
       <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.04</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
         <v>3.08</v>
@@ -1880,16 +1880,16 @@
         <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
         <v>1.76</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="O10" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="P10" t="n">
-        <v>10.3</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2315,28 +2315,28 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="O12" t="n">
-        <v>3.97</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>4.04</v>
+        <v>3.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
         <v>2.33</v>
       </c>
       <c r="S12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="V12" t="n">
         <v>1.53</v>
@@ -2348,16 +2348,16 @@
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
         <v>2.4</v>
@@ -2372,7 +2372,7 @@
         <v>1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK12" t="n">
         <v>1.85</v>
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2636,25 +2636,25 @@
         <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>5.41</v>
+        <v>4.95</v>
       </c>
       <c r="P14" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T14" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
         <v>1.75</v>
@@ -2666,31 +2666,31 @@
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.5</v>
+        <v>6.28</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AE14" t="n">
         <v>1.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,31 +2792,31 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="O15" t="n">
-        <v>3.83</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
         <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S15" t="n">
         <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W15" t="n">
         <v>1.14</v>
@@ -2825,25 +2825,25 @@
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF15" t="n">
         <v>1.44</v>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AK15" t="n">
         <v>1.4</v>
@@ -2951,31 +2951,31 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>5.08</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>6.91</v>
+        <v>5.4</v>
       </c>
       <c r="Q16" t="n">
         <v>1.89</v>
       </c>
       <c r="R16" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="S16" t="n">
         <v>1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U16" t="n">
         <v>1.95</v>
       </c>
       <c r="V16" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="W16" t="n">
         <v>1.17</v>
@@ -2990,22 +2990,22 @@
         <v>5.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB16" t="n">
         <v>2.88</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE16" t="n">
         <v>1.3</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
         <v>2.4</v>
@@ -3024,7 +3024,7 @@
         <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1520,58 +1520,58 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.8</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.56</v>
-      </c>
       <c r="U7" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
         <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF7" t="n">
         <v>1.75</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="P8" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC8" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.29</v>
+        <v>3.55</v>
       </c>
       <c r="P9" t="n">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.05</v>
+        <v>2.46</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="T9" t="n">
-        <v>2.69</v>
+        <v>3.12</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.05</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AE9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="P13" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="R13" t="n">
         <v>1.78</v>
       </c>
       <c r="S13" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="T13" t="n">
-        <v>2.24</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1700,22 +1700,22 @@
         <v>2.69</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA8" t="n">
         <v>2.05</v>
@@ -1724,13 +1724,13 @@
         <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
         <v>1.76</v>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AK8" t="n">
         <v>1.53</v>
@@ -1847,16 +1847,16 @@
         <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="R9" t="n">
         <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
         <v>2.62</v>
@@ -1865,16 +1865,16 @@
         <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="AA9" t="n">
         <v>1.83</v>
@@ -1889,10 +1889,10 @@
         <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
         <v>2.05</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="P14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.63</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.82</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>4.95</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>1.84</v>
       </c>
       <c r="R15" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>5</v>
+        <v>6.28</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AG15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK15" t="n">
         <v>2.63</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O7" t="n">
         <v>3.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Q7" t="n">
         <v>3.3</v>
@@ -1544,7 +1544,7 @@
         <v>2.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
         <v>1.06</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2483,7 +2483,7 @@
         <v>3.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="R13" t="n">
         <v>1.78</v>
@@ -2547,7 +2547,7 @@
         <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="O5" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="R5" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="S5" t="n">
         <v>1.23</v>
@@ -1223,13 +1223,13 @@
         <v>3.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
         <v>1.02</v>
@@ -1238,28 +1238,28 @@
         <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
         <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S7" t="n">
         <v>1.36</v>
@@ -1541,7 +1541,7 @@
         <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V7" t="n">
         <v>1.36</v>
@@ -1565,13 +1565,13 @@
         <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.83</v>
+        <v>3.28</v>
       </c>
       <c r="AD7" t="n">
         <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
         <v>1.75</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.29</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.05</v>
+        <v>2.54</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG8" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>2.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.54</v>
+        <v>3.05</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z9" t="n">
         <v>3.2</v>
       </c>
-      <c r="U9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.74</v>
-      </c>
       <c r="AA9" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2483,7 +2483,7 @@
         <v>3.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="R13" t="n">
         <v>1.78</v>
@@ -2547,7 +2547,7 @@
         <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1526,7 +1526,7 @@
         <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
         <v>3.3</v>
@@ -1682,7 +1682,7 @@
         <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
         <v>3.6</v>
@@ -1736,7 +1736,7 @@
         <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA9" t="n">
         <v>2.05</v>
@@ -1886,7 +1886,7 @@
         <v>3.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
         <v>1.08</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2315,25 +2315,25 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T12" t="n">
         <v>3.25</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.3</v>
       </c>
       <c r="U12" t="n">
         <v>2.44</v>
@@ -2345,34 +2345,34 @@
         <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="O13" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q13" t="n">
         <v>2.96</v>
@@ -2504,7 +2504,7 @@
         <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y13" t="n">
         <v>1.35</v>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK13" t="n">
         <v>1.6</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.82</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.7</v>
+        <v>4.95</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="S14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AG14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK14" t="n">
         <v>2.63</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="P15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2.63</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,40 +2951,40 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P16" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="Q16" t="n">
         <v>1.89</v>
       </c>
       <c r="R16" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T16" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
         <v>1.95</v>
       </c>
       <c r="V16" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z16" t="n">
         <v>5.8</v>
@@ -2996,13 +2996,13 @@
         <v>2.88</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
         <v>1.53</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1211,7 +1211,7 @@
         <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="R5" t="n">
         <v>2.44</v>
@@ -1232,13 +1232,13 @@
         <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
         <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.1</v>
+        <v>5.92</v>
       </c>
       <c r="AA5" t="n">
         <v>1.47</v>
@@ -1526,10 +1526,10 @@
         <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="R7" t="n">
         <v>1.98</v>
@@ -1544,25 +1544,25 @@
         <v>2.88</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.48</v>
+        <v>3.53</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>3.28</v>
@@ -1574,7 +1574,7 @@
         <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG7" t="n">
         <v>1.95</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC8" t="n">
         <v>3.5</v>
       </c>
-      <c r="P8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AD8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z8" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.05</v>
+        <v>2.53</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.89</v>
+        <v>2.53</v>
       </c>
       <c r="V9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.36</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AE9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="O11" t="n">
-        <v>5.6</v>
+        <v>3.08</v>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
+        <v>3.32</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O12" t="n">
         <v>3.5</v>
@@ -2330,16 +2330,16 @@
         <v>2.35</v>
       </c>
       <c r="S12" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T12" t="n">
         <v>3.25</v>
       </c>
       <c r="U12" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.1</v>
@@ -2348,13 +2348,13 @@
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB12" t="n">
         <v>2.2</v>
@@ -2369,10 +2369,10 @@
         <v>1.16</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S13" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
         <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W13" t="n">
         <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AB13" t="n">
         <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF13" t="n">
         <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
-        <v>4.95</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="S14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.2</v>
       </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="AF14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.35</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.63</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.82</v>
+        <v>1.48</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>4.95</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>5.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="S15" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AG15" t="n">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.4</v>
+        <v>2.63</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="O16" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="P16" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
         <v>1.89</v>
@@ -2969,13 +2969,13 @@
         <v>1.17</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U16" t="n">
         <v>1.95</v>
       </c>
       <c r="V16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W16" t="n">
         <v>1.2</v>
@@ -2984,13 +2984,13 @@
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z16" t="n">
         <v>5.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB16" t="n">
         <v>2.88</v>
@@ -2999,16 +2999,16 @@
         <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>1.12</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.85</v>
+        <v>2.53</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>2.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.53</v>
+        <v>2.85</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="U9" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AE9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>1.48</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>4.95</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>5.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="S14" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AG14" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.35</v>
+        <v>2.63</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.48</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>4.95</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>5.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="S15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.2</v>
       </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="AF15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.35</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2.63</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.61</v>
+        <v>2.03</v>
       </c>
       <c r="O6" t="n">
-        <v>4.26</v>
+        <v>3.62</v>
       </c>
       <c r="P6" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
         <v>2.25</v>
@@ -1544,7 +1544,7 @@
         <v>2.88</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
         <v>1.07</v>
@@ -1553,28 +1553,28 @@
         <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" t="n">
         <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
         <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG7" t="n">
         <v>1.95</v>
@@ -1593,7 +1593,7 @@
         <v>1.32</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1685,7 +1685,7 @@
         <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q8" t="n">
         <v>2.53</v>
@@ -1700,16 +1700,16 @@
         <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.53</v>
+        <v>2.77</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
         <v>1.25</v>
@@ -1727,10 +1727,10 @@
         <v>3.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
         <v>1.7</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,16 +1838,16 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="O9" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="P9" t="n">
-        <v>2.99</v>
+        <v>2.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
         <v>2.1</v>
@@ -1868,7 +1868,7 @@
         <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
         <v>1.3</v>
@@ -1883,7 +1883,7 @@
         <v>1.81</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD9" t="n">
         <v>1.25</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
         <v>1.55</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.32</v>
+        <v>2.24</v>
       </c>
       <c r="O10" t="n">
-        <v>5.2</v>
+        <v>3.08</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>3.32</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.24</v>
+        <v>1.32</v>
       </c>
       <c r="O11" t="n">
-        <v>3.08</v>
+        <v>5.2</v>
       </c>
       <c r="P11" t="n">
-        <v>3.32</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
         <v>1.91</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
         <v>3.4</v>
@@ -2330,49 +2330,49 @@
         <v>2.35</v>
       </c>
       <c r="S12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
         <v>3.25</v>
       </c>
       <c r="U12" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W12" t="n">
         <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z12" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2483,13 +2483,13 @@
         <v>3.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="T13" t="n">
         <v>2.7</v>
@@ -2498,7 +2498,7 @@
         <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
         <v>1.06</v>
@@ -2507,10 +2507,10 @@
         <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.23</v>
+        <v>3.01</v>
       </c>
       <c r="AA13" t="n">
         <v>2.16</v>
@@ -2519,19 +2519,19 @@
         <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.6</v>
+        <v>4.59</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK13" t="n">
         <v>1.57</v>
@@ -2633,19 +2633,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
         <v>4.95</v>
       </c>
       <c r="P14" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q14" t="n">
         <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="S14" t="n">
         <v>1.2</v>
@@ -2654,13 +2654,13 @@
         <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
@@ -2672,7 +2672,7 @@
         <v>6.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB14" t="n">
         <v>2.76</v>
@@ -2681,13 +2681,13 @@
         <v>1.98</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE14" t="n">
         <v>1.34</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
         <v>2.45</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="P15" t="n">
         <v>2.2</v>
@@ -2810,13 +2810,13 @@
         <v>1.24</v>
       </c>
       <c r="T15" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="V15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W15" t="n">
         <v>1.17</v>
@@ -2825,22 +2825,22 @@
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>5</v>
+        <v>5.29</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC15" t="n">
         <v>2.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE15" t="n">
         <v>1.2</v>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
         <v>1.35</v>
@@ -2951,31 +2951,31 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="O16" t="n">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="R16" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U16" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="V16" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W16" t="n">
         <v>1.2</v>
@@ -2984,31 +2984,31 @@
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AC16" t="n">
         <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AE16" t="n">
         <v>1.3</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="O5" t="n">
         <v>4.05</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q5" t="n">
         <v>2.11</v>
@@ -1217,10 +1217,10 @@
         <v>2.44</v>
       </c>
       <c r="S5" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
         <v>2.14</v>
@@ -1235,7 +1235,7 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
         <v>5.92</v>
@@ -1256,7 +1256,7 @@
         <v>1.24</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG5" t="n">
         <v>2.55</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.24</v>
+        <v>1.32</v>
       </c>
       <c r="O10" t="n">
-        <v>3.08</v>
+        <v>5.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.32</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.32</v>
+        <v>1.93</v>
       </c>
       <c r="O11" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="P8" t="n">
-        <v>3.45</v>
+        <v>2.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="U8" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.31</v>
       </c>
       <c r="AE8" t="n">
         <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE9" t="n">
         <v>1.08</v>
       </c>
       <c r="AF9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.32</v>
+        <v>1.93</v>
       </c>
       <c r="O10" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.93</v>
+        <v>1.32</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="P11" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>4.95</v>
+        <v>3.76</v>
       </c>
       <c r="P14" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="S14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.2</v>
       </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.6</v>
+        <v>1.35</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.76</v>
+        <v>4.95</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="S15" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.29</v>
+        <v>6.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.29</v>
+        <v>1.98</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.35</v>
+        <v>2.6</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="R6" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S6" t="n">
         <v>1.2</v>
@@ -1400,7 +1400,7 @@
         <v>5.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AB6" t="n">
         <v>2.6</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,25 +1520,25 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.66</v>
+        <v>3.78</v>
       </c>
       <c r="R7" t="n">
         <v>1.98</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
         <v>2.88</v>
@@ -1562,13 +1562,13 @@
         <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
         <v>1.1</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.38</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE8" t="n">
         <v>1.08</v>
       </c>
       <c r="AF8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.55</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="P9" t="n">
-        <v>3.45</v>
+        <v>2.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="U9" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.31</v>
       </c>
       <c r="AE9" t="n">
         <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,37 +1997,37 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="Q10" t="n">
         <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S10" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
         <v>1.24</v>
@@ -2036,25 +2036,25 @@
         <v>3.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
         <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -2483,25 +2483,25 @@
         <v>3.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="S13" t="n">
         <v>1.52</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="V13" t="n">
         <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.05</v>
@@ -2510,28 +2510,28 @@
         <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.76</v>
+        <v>4.95</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="S14" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.29</v>
+        <v>6.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.29</v>
+        <v>1.98</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.35</v>
+        <v>2.6</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
-        <v>4.95</v>
+        <v>3.76</v>
       </c>
       <c r="P15" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="S15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.2</v>
       </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.6</v>
+        <v>1.35</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1208,10 +1208,10 @@
         <v>4.05</v>
       </c>
       <c r="P5" t="n">
-        <v>3.9</v>
+        <v>3.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="R5" t="n">
         <v>2.44</v>
@@ -1235,19 +1235,19 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.92</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AD5" t="n">
         <v>1.69</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="P8" t="n">
-        <v>3.45</v>
+        <v>2.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="U8" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.31</v>
       </c>
       <c r="AE8" t="n">
         <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE9" t="n">
         <v>1.08</v>
       </c>
       <c r="AF9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.98</v>
+        <v>1.32</v>
       </c>
       <c r="O10" t="n">
-        <v>2.93</v>
+        <v>5.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.02</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.32</v>
+        <v>1.98</v>
       </c>
       <c r="O11" t="n">
-        <v>5.2</v>
+        <v>2.93</v>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
+        <v>3.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="O5" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P5" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="R5" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="S5" t="n">
         <v>1.2</v>
@@ -1223,7 +1223,7 @@
         <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V5" t="n">
         <v>1.66</v>
@@ -1232,7 +1232,7 @@
         <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
         <v>1.13</v>
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AD5" t="n">
         <v>1.69</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1370,10 +1370,10 @@
         <v>2.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="R6" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="S6" t="n">
         <v>1.2</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
         <v>3.78</v>
@@ -1544,7 +1544,7 @@
         <v>2.88</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
         <v>1.07</v>
@@ -1553,16 +1553,16 @@
         <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
         <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>3.51</v>
@@ -1571,7 +1571,7 @@
         <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
         <v>1.75</v>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
         <v>1.32</v>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S8" t="n">
         <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
         <v>3.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
         <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="P9" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="V9" t="n">
         <v>1.43</v>
@@ -1868,31 +1868,31 @@
         <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
         <v>2.05</v>
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="P10" t="n">
         <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,34 +2156,34 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="O11" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="R11" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="S11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.36</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.41</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
@@ -2195,13 +2195,13 @@
         <v>3.34</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="AD11" t="n">
         <v>1.29</v>
@@ -2210,10 +2210,10 @@
         <v>1.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,46 +2315,46 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
         <v>3.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="R12" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="S12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T12" t="n">
         <v>3.25</v>
       </c>
       <c r="U12" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V12" t="n">
         <v>1.54</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB12" t="n">
         <v>2.25</v>
@@ -2363,13 +2363,13 @@
         <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AE12" t="n">
         <v>1.18</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
         <v>2.3</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q13" t="n">
         <v>2.7</v>
@@ -2489,28 +2489,28 @@
         <v>1.81</v>
       </c>
       <c r="S13" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T13" t="n">
-        <v>2.29</v>
+        <v>2.69</v>
       </c>
       <c r="U13" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA13" t="n">
         <v>2.2</v>
@@ -2519,19 +2519,19 @@
         <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.58</v>
+        <v>4.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>2.62</v>
       </c>
       <c r="O14" t="n">
-        <v>4.95</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="U14" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.25</v>
+        <v>5.29</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,65 +2792,65 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2.95</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG15" t="n">
         <v>2.4</v>
       </c>
-      <c r="AC15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.58</v>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.35</v>
+        <v>2.7</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="O16" t="n">
-        <v>4.55</v>
+        <v>4.85</v>
       </c>
       <c r="P16" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q16" t="n">
         <v>1.85</v>
@@ -2975,7 +2975,7 @@
         <v>2.04</v>
       </c>
       <c r="V16" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="W16" t="n">
         <v>1.2</v>
@@ -2993,22 +2993,22 @@
         <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.75</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="P2" t="n">
-        <v>4.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>4.68</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>10.2</v>
+        <v>4.05</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.85</v>
+        <v>1.31</v>
       </c>
       <c r="O4" t="n">
-        <v>3.05</v>
+        <v>4.68</v>
       </c>
       <c r="P4" t="n">
-        <v>2.35</v>
+        <v>10.2</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="U8" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.33</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AE8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.54</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R9" t="n">
         <v>2.03</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.13</v>
-      </c>
       <c r="S9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2318,10 +2318,10 @@
         <v>1.96</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
         <v>2.37</v>
@@ -2330,31 +2330,31 @@
         <v>2.32</v>
       </c>
       <c r="S12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U12" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB12" t="n">
         <v>2.25</v>
@@ -2363,13 +2363,13 @@
         <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
         <v>2.3</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.62</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.05</v>
+        <v>1.84</v>
       </c>
       <c r="R14" t="n">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="S14" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.13</v>
       </c>
-      <c r="Z14" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK14" t="n">
-        <v>1.36</v>
+        <v>2.62</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.45</v>
+        <v>2.51</v>
       </c>
       <c r="O15" t="n">
-        <v>4.95</v>
+        <v>3.71</v>
       </c>
       <c r="P15" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>3.07</v>
       </c>
       <c r="R15" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>1.58</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>4.85</v>
+        <v>4.55</v>
       </c>
       <c r="P16" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q16" t="n">
         <v>1.85</v>
       </c>
       <c r="R16" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="S16" t="n">
         <v>1.2</v>
@@ -2972,13 +2972,13 @@
         <v>4.33</v>
       </c>
       <c r="U16" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="V16" t="n">
         <v>1.87</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
@@ -2987,7 +2987,7 @@
         <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AA16" t="n">
         <v>1.36</v>
@@ -2996,10 +2996,10 @@
         <v>2.88</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE16" t="n">
         <v>1.33</v>
@@ -3008,7 +3008,7 @@
         <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.75</v>
+        <v>1.31</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>4.68</v>
       </c>
       <c r="P3" t="n">
-        <v>4.05</v>
+        <v>10.2</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="O4" t="n">
-        <v>4.68</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>10.2</v>
+        <v>4.05</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R8" t="n">
         <v>2.03</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.13</v>
-      </c>
       <c r="S8" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.33</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AE9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.54</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,31 +2633,31 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.44</v>
+        <v>2.51</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>3.71</v>
       </c>
       <c r="P14" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.84</v>
+        <v>3.07</v>
       </c>
       <c r="R14" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U14" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="W14" t="n">
         <v>1.17</v>
@@ -2666,31 +2666,31 @@
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.13</v>
+        <v>1.58</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,31 +2792,31 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.51</v>
+        <v>1.44</v>
       </c>
       <c r="O15" t="n">
-        <v>3.71</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.07</v>
+        <v>1.84</v>
       </c>
       <c r="R15" t="n">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="W15" t="n">
         <v>1.17</v>
@@ -2825,31 +2825,31 @@
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.58</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.4</v>
+        <v>2.62</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>4.68</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>10.2</v>
+        <v>4.05</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.75</v>
+        <v>1.31</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>4.68</v>
       </c>
       <c r="P4" t="n">
-        <v>4.05</v>
+        <v>10.2</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="O2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>4.75</v>
       </c>
       <c r="P3" t="n">
-        <v>4.05</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="O4" t="n">
-        <v>4.68</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>10.2</v>
+        <v>4.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1208,13 +1208,13 @@
         <v>4.2</v>
       </c>
       <c r="P5" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="R5" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="S5" t="n">
         <v>1.2</v>
@@ -1223,37 +1223,37 @@
         <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W5" t="n">
         <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF5" t="n">
         <v>1.44</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1364,10 +1364,10 @@
         <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
         <v>2.54</v>
@@ -1376,49 +1376,49 @@
         <v>2.32</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z6" t="n">
         <v>5.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB6" t="n">
         <v>2.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AD6" t="n">
         <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
         <v>1.64</v>
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
         <v>1.98</v>
@@ -1544,10 +1544,10 @@
         <v>2.88</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
         <v>1.05</v>
@@ -1562,10 +1562,10 @@
         <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="AD7" t="n">
         <v>1.27</v>
@@ -1679,28 +1679,28 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.8</v>
-      </c>
       <c r="R8" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
         <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
         <v>1.33</v>
@@ -1712,10 +1712,10 @@
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
         <v>2.09</v>
@@ -1724,19 +1724,19 @@
         <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
         <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,58 +1838,58 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q9" t="n">
         <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
         <v>1.37</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="U9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
         <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
         <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
         <v>2.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
         <v>1.65</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
         <v>1.75</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="O10" t="n">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>4.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>2.61</v>
       </c>
       <c r="R10" t="n">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="S10" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.73</v>
       </c>
       <c r="V10" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.75</v>
+        <v>3.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.43</v>
+        <v>1.94</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.46</v>
+        <v>1.89</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.13</v>
+        <v>3.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="P11" t="n">
-        <v>3.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.43</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="S11" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="U11" t="n">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.34</v>
+        <v>5.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.35</v>
+        <v>2.29</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="O12" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="P12" t="n">
         <v>3.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="R12" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V12" t="n">
         <v>1.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2480,55 +2480,55 @@
         <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="Q13" t="n">
         <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
         <v>1.44</v>
       </c>
       <c r="T13" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="U13" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="V13" t="n">
         <v>1.32</v>
       </c>
       <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
         <v>1.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AB13" t="n">
         <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.2</v>
+        <v>3.87</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
         <v>1.83</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.51</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.71</v>
+        <v>4.98</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="S14" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.58</v>
+        <v>1.13</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.4</v>
+        <v>2.85</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,31 +2792,31 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.44</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>3.71</v>
       </c>
       <c r="P15" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.84</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="W15" t="n">
         <v>1.17</v>
@@ -2825,31 +2825,31 @@
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>7</v>
+        <v>5.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.62</v>
+        <v>1.41</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2954,28 +2954,28 @@
         <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="P16" t="n">
-        <v>4.8</v>
+        <v>5.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="R16" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T16" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="W16" t="n">
         <v>1.18</v>
@@ -2984,10 +2984,10 @@
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="AA16" t="n">
         <v>1.36</v>
@@ -2996,19 +2996,19 @@
         <v>2.88</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF16" t="n">
         <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.05</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.37</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.82</v>
+        <v>1.75</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>2.32</v>
+        <v>4.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.64</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.95</v>
+        <v>2.22</v>
       </c>
       <c r="S2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T2" t="n">
-        <v>2.47</v>
+        <v>2.85</v>
       </c>
       <c r="U2" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="V2" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
         <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.32</v>
+        <v>1.91</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>2.82</v>
       </c>
       <c r="O3" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>3.64</v>
       </c>
       <c r="R3" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="S3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.38</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.29</v>
-      </c>
       <c r="Z3" t="n">
-        <v>3.59</v>
+        <v>2.91</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.1</v>
+        <v>1.32</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>4.75</v>
       </c>
       <c r="P4" t="n">
-        <v>4.05</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="S4" t="n">
         <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="U4" t="n">
         <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
         <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>2.38</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.88</v>
+        <v>1.47</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1523,7 +1523,7 @@
         <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
         <v>2.2</v>
@@ -1544,19 +1544,19 @@
         <v>2.88</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
         <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" t="n">
         <v>2</v>
@@ -1571,7 +1571,7 @@
         <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF7" t="n">
         <v>1.75</v>
@@ -1593,7 +1593,7 @@
         <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.37</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U9" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.05</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="n">
         <v>2.7</v>
@@ -2492,7 +2492,7 @@
         <v>1.44</v>
       </c>
       <c r="T13" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
         <v>3.15</v>
@@ -2507,10 +2507,10 @@
         <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.23</v>
+        <v>3.01</v>
       </c>
       <c r="AA13" t="n">
         <v>2.16</v>
@@ -2519,10 +2519,10 @@
         <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
         <v>1.06</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>4.75</v>
       </c>
       <c r="P2" t="n">
-        <v>4.05</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="S2" t="n">
         <v>1.38</v>
       </c>
       <c r="T2" t="n">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="U2" t="n">
         <v>2.75</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
         <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.79</v>
+        <v>2.38</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.88</v>
+        <v>1.47</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.82</v>
+        <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>2.32</v>
+        <v>4.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.64</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>1.95</v>
+        <v>2.22</v>
       </c>
       <c r="S3" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T3" t="n">
-        <v>2.47</v>
+        <v>2.85</v>
       </c>
       <c r="U3" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.32</v>
+        <v>1.91</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>2.82</v>
       </c>
       <c r="O4" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>9.800000000000001</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>3.64</v>
       </c>
       <c r="R4" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="S4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.38</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.29</v>
-      </c>
       <c r="Z4" t="n">
-        <v>3.59</v>
+        <v>2.91</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.1</v>
+        <v>1.32</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1364,16 +1364,16 @@
         <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="R6" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S6" t="n">
         <v>1.22</v>
@@ -1382,10 +1382,10 @@
         <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W6" t="n">
         <v>1.17</v>
@@ -1400,7 +1400,7 @@
         <v>5.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB6" t="n">
         <v>2.6</v>
@@ -1415,10 +1415,10 @@
         <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="P7" t="n">
         <v>2.2</v>
@@ -1532,19 +1532,19 @@
         <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="U7" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
         <v>1.05</v>
@@ -1553,19 +1553,19 @@
         <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="AD7" t="n">
         <v>1.27</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.93</v>
+        <v>1.23</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="P10" t="n">
-        <v>4.09</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.61</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="S10" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="U10" t="n">
-        <v>2.73</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.34</v>
+        <v>5.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.35</v>
+        <v>2.29</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.23</v>
       </c>
-      <c r="O11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AK11" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -2489,13 +2489,13 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="U13" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
         <v>1.32</v>
@@ -2504,22 +2504,22 @@
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
         <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AB13" t="n">
         <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="AD13" t="n">
         <v>1.2</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>4.98</v>
+        <v>3.71</v>
       </c>
       <c r="P14" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="S14" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="U14" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.75</v>
+        <v>5.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.85</v>
+        <v>1.41</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.71</v>
+        <v>4.98</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T15" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.35</v>
+        <v>6.75</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AG15" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.57</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.41</v>
+        <v>2.85</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.27</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>9.800000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.38</v>
       </c>
-      <c r="T2" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V2" t="n">
+      <c r="Z2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK2" t="n">
         <v>1.36</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>3.1</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P3" t="n">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="Q3" t="n">
         <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
         <v>1.38</v>
@@ -908,7 +908,7 @@
         <v>2.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
         <v>1.06</v>
@@ -920,13 +920,13 @@
         <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="AA3" t="n">
         <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
         <v>3.4</v>
@@ -935,13 +935,13 @@
         <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.82</v>
+        <v>1.31</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.64</v>
+        <v>1.79</v>
       </c>
       <c r="R4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.95</v>
       </c>
-      <c r="S4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC4" t="n">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.32</v>
+        <v>3.1</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="O5" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="P5" t="n">
         <v>4.2</v>
       </c>
-      <c r="P5" t="n">
-        <v>3.83</v>
-      </c>
       <c r="Q5" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="R5" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="S5" t="n">
         <v>1.2</v>
@@ -1223,43 +1223,43 @@
         <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
         <v>1.64</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AC5" t="n">
         <v>2.16</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1382,13 +1382,13 @@
         <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
@@ -1409,7 +1409,7 @@
         <v>2.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE6" t="n">
         <v>1.25</v>
@@ -1418,7 +1418,7 @@
         <v>1.38</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
         <v>3.21</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
         <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>1.41</v>
@@ -1541,10 +1541,10 @@
         <v>2.59</v>
       </c>
       <c r="U7" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
         <v>1.05</v>
@@ -1553,22 +1553,22 @@
         <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>3.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE7" t="n">
         <v>1.09</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T9" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>2.6</v>
+        <v>3.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC9" t="n">
         <v>3.6</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AD9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AG9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
         <v>5.2</v>
@@ -2012,28 +2012,28 @@
         <v>2.55</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.13</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z10" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA10" t="n">
         <v>1.5</v>
@@ -2042,19 +2042,19 @@
         <v>2.28</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AD10" t="n">
         <v>1.54</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2159,19 +2159,19 @@
         <v>1.93</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>4.09</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="R11" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="S11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
         <v>3</v>
@@ -2180,31 +2180,31 @@
         <v>2.65</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
         <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
         <v>1.07</v>
@@ -2229,7 +2229,7 @@
         <v>1.23</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="O12" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="Q12" t="n">
         <v>2.45</v>
@@ -2330,34 +2330,34 @@
         <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T12" t="n">
         <v>3.34</v>
       </c>
       <c r="U12" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.5</v>
+        <v>4.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
         <v>2.39</v>
@@ -2366,10 +2366,10 @@
         <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
         <v>2.23</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
         <v>1.85</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1</v>
+        <v>3.88</v>
       </c>
       <c r="Q13" t="n">
         <v>2.7</v>
@@ -2489,10 +2489,10 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="U13" t="n">
         <v>3</v>
@@ -2504,22 +2504,22 @@
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
         <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="AA13" t="n">
         <v>2.18</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="AD13" t="n">
         <v>1.2</v>
@@ -2528,10 +2528,10 @@
         <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2639,16 +2639,16 @@
         <v>3.71</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
         <v>2.4</v>
       </c>
       <c r="S14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
         <v>3.75</v>
@@ -2663,25 +2663,25 @@
         <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
         <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="AA14" t="n">
         <v>1.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE14" t="n">
         <v>1.23</v>
@@ -2690,7 +2690,7 @@
         <v>1.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AK14" t="n">
         <v>1.41</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="O15" t="n">
-        <v>4.98</v>
+        <v>4.92</v>
       </c>
       <c r="P15" t="n">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="Q15" t="n">
         <v>1.8</v>
@@ -2813,28 +2813,28 @@
         <v>4.33</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="V15" t="n">
         <v>1.78</v>
       </c>
       <c r="W15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z15" t="n">
         <v>6.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="AC15" t="n">
         <v>2</v>
@@ -2954,10 +2954,10 @@
         <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5.55</v>
+        <v>5.25</v>
       </c>
       <c r="Q16" t="n">
         <v>1.9</v>
@@ -2972,10 +2972,10 @@
         <v>4.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W16" t="n">
         <v>1.18</v>
@@ -2987,28 +2987,28 @@
         <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AA16" t="n">
         <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE16" t="n">
         <v>1.28</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>1.31</v>
       </c>
       <c r="O3" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="P3" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>1.79</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T3" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="U3" t="n">
         <v>2.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
         <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>2.41</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.31</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.79</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="U4" t="n">
         <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
         <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.41</v>
+        <v>1.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W6" t="n">
         <v>1.18</v>
@@ -1409,7 +1409,7 @@
         <v>2.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
         <v>1.25</v>
@@ -1418,7 +1418,7 @@
         <v>1.38</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="O10" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>9.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>2.57</v>
       </c>
       <c r="R10" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.35</v>
+        <v>1.78</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.93</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="P11" t="n">
-        <v>3.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.57</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="S11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="U11" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="W11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.06</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.78</v>
+        <v>3.35</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC8" t="n">
         <v>3.6</v>
       </c>
-      <c r="P8" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="AD8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.36</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>3.01</v>
+        <v>2.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>1.48</v>
       </c>
       <c r="O14" t="n">
-        <v>3.71</v>
+        <v>4.92</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>5.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="S14" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T14" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="V14" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.45</v>
+        <v>6.75</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AG14" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.41</v>
+        <v>2.85</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.48</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>4.92</v>
+        <v>3.71</v>
       </c>
       <c r="P15" t="n">
-        <v>5.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T15" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.75</v>
+        <v>5.45</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.4</v>
       </c>
-      <c r="AB15" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG15" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.85</v>
+        <v>1.41</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.93</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.57</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="U10" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.06</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.78</v>
+        <v>3.35</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="O11" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>9.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.65</v>
+        <v>2.57</v>
       </c>
       <c r="R11" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="V11" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.35</v>
+        <v>1.78</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.48</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>4.92</v>
+        <v>3.71</v>
       </c>
       <c r="P14" t="n">
-        <v>5.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="S14" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.75</v>
+        <v>5.45</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.4</v>
       </c>
-      <c r="AB14" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG14" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.85</v>
+        <v>1.41</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>1.48</v>
       </c>
       <c r="O15" t="n">
-        <v>3.71</v>
+        <v>4.92</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>5.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="S15" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T15" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="V15" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.45</v>
+        <v>6.75</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AG15" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.41</v>
+        <v>2.85</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.31</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.79</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T3" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="U3" t="n">
         <v>2.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
         <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.41</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>1.31</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="P4" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>1.79</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T4" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="U4" t="n">
         <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
         <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.78</v>
+        <v>2.41</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1361,34 +1361,34 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="S6" t="n">
         <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V6" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
@@ -1397,28 +1397,28 @@
         <v>1.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.6</v>
+        <v>5.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC6" t="n">
         <v>2.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AE6" t="n">
         <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>1.48</v>
       </c>
       <c r="O14" t="n">
-        <v>3.71</v>
+        <v>4.92</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>5.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="S14" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T14" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="V14" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.45</v>
+        <v>6.75</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AG14" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.41</v>
+        <v>2.85</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.48</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>4.92</v>
+        <v>3.71</v>
       </c>
       <c r="P15" t="n">
-        <v>5.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T15" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.75</v>
+        <v>5.45</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.4</v>
       </c>
-      <c r="AB15" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG15" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.85</v>
+        <v>1.41</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,139 +693,139 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S2" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6</v>
+        <v>2.89</v>
       </c>
       <c r="U2" t="n">
-        <v>3.08</v>
+        <v>2.71</v>
       </c>
       <c r="V2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>['19', '51']</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
         <v>1.29</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK2" t="n">
-        <v>1.36</v>
+        <v>1.86</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46219.5</v>
@@ -852,139 +852,139 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>2.67</v>
       </c>
       <c r="O3" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="P3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC3" t="n">
         <v>3.85</v>
       </c>
-      <c r="Q3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V3" t="n">
+      <c r="AD3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>['14', '61', '64']</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.36</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46219.5</v>
@@ -1020,130 +1020,130 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="O4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S4" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="U4" t="n">
         <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.21</v>
+        <v>2.91</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['83', '86']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
         <v>1.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46219.5</v>
@@ -1179,33 +1179,33 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O5" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="P5" t="n">
         <v>4.2</v>
@@ -1214,95 +1214,95 @@
         <v>2.15</v>
       </c>
       <c r="R5" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="V5" t="n">
         <v>1.64</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39', '42', '45+1', '53', '83', '89']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46219.58333333334</v>
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O7" t="n">
         <v>3.1</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.21</v>
-      </c>
       <c r="P7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2.23</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AB7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC7" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="AG7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S8" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U8" t="n">
-        <v>3.01</v>
+        <v>2.65</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z8" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R9" t="n">
         <v>2.05</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.15</v>
       </c>
       <c r="S9" t="n">
         <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>2.6</v>
+        <v>3.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="AA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="O10" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>9.699999999999999</v>
+        <v>4.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>2.62</v>
       </c>
       <c r="R10" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.35</v>
+        <v>1.77</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.93</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
       <c r="P11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
       <c r="U11" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.06</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.78</v>
+        <v>3.42</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="P12" t="n">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
         <v>3.34</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W12" t="n">
         <v>1.11</v>
@@ -2348,10 +2348,10 @@
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.62</v>
+        <v>4.3</v>
       </c>
       <c r="AA12" t="n">
         <v>1.62</v>
@@ -2360,19 +2360,19 @@
         <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AE12" t="n">
         <v>1.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2477,61 +2477,61 @@
         <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="P13" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T13" t="n">
-        <v>2.66</v>
+        <v>2.27</v>
       </c>
       <c r="U13" t="n">
         <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
         <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="AD13" t="n">
         <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="Q14" t="n">
         <v>1.8</v>
@@ -2648,7 +2648,7 @@
         <v>2.7</v>
       </c>
       <c r="S14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
         <v>4.33</v>
@@ -2669,28 +2669,28 @@
         <v>1.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA14" t="n">
         <v>1.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.07</v>
+        <v>2.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF14" t="n">
         <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>2.51</v>
       </c>
       <c r="O15" t="n">
         <v>3.71</v>
@@ -2801,55 +2801,55 @@
         <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S15" t="n">
         <v>1.22</v>
       </c>
       <c r="T15" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="V15" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF15" t="n">
         <v>1.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P16" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R16" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="S16" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V16" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB16" t="n">
         <v>2.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AD16" t="n">
         <v>1.75</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,28 +693,28 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -725,107 +725,107 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.95</v>
+        <v>1.28</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="P2" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="R2" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="S2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T2" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="U2" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.72</v>
+        <v>2.24</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>['19', '51']</t>
+          <t>['83', '86']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.86</v>
+        <v>3.45</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AN2" t="n">
         <v>4</v>
       </c>
       <c r="AO2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AP2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.73</v>
+        <v>1.68</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AS2" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="AT2" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46219.5</v>
@@ -852,31 +852,31 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -884,107 +884,107 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.67</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.62</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S3" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T3" t="n">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="U3" t="n">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="V3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
         <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['19', '51']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>['14', '61', '64']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.36</v>
+        <v>1.86</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AP3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.26</v>
+        <v>0.73</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.64</v>
+        <v>1.09</v>
       </c>
       <c r="AS3" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="AT3" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46219.5</v>
@@ -1011,139 +1011,139 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.28</v>
+        <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>4.8</v>
+        <v>2.94</v>
       </c>
       <c r="P4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>['14', '61', '64']</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="n">
         <v>9</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>['83', '86']</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>['8']</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>14</v>
       </c>
-      <c r="AP4" t="n">
-        <v>10</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="AS4" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="AT4" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46219.5</v>
@@ -1338,26 +1338,26 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36', '71', '88']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
@@ -1440,28 +1440,28 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46219.66666666666</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="S7" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="T7" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="U7" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.34</v>
+        <v>4.18</v>
       </c>
       <c r="AD7" t="n">
         <v>1.19</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R8" t="n">
         <v>2.05</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.13</v>
       </c>
       <c r="S8" t="n">
         <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>2.65</v>
+        <v>3.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="S9" t="n">
         <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U9" t="n">
-        <v>3.01</v>
+        <v>2.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
         <v>2.99</v>
       </c>
       <c r="P13" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="Q13" t="n">
         <v>2.88</v>
@@ -2489,49 +2489,49 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y13" t="n">
         <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD13" t="n">
         <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.44</v>
       </c>
-      <c r="O14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="AB14" t="n">
         <v>2.7</v>
       </c>
-      <c r="S14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.4</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG14" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.7</v>
+        <v>1.46</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.51</v>
+        <v>1.44</v>
       </c>
       <c r="O15" t="n">
-        <v>3.71</v>
+        <v>4.5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>4.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.14</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="S15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T15" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="U15" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="W15" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK15" t="n">
         <v>2.7</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.46</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-16.xlsx
+++ b/jogos_2026-07-16.xlsx
@@ -693,139 +693,139 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
         <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>2</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.28</v>
+        <v>2.67</v>
       </c>
       <c r="O2" t="n">
-        <v>4.8</v>
+        <v>2.94</v>
       </c>
       <c r="P2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>['14', '61', '64']</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO2" t="n">
         <v>9</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>['83', '86']</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>['8']</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>14</v>
       </c>
-      <c r="AP2" t="n">
-        <v>10</v>
-      </c>
       <c r="AQ2" t="n">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="AS2" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="AT2" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46219.5</v>
@@ -1011,139 +1011,139 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC4" t="n">
-        <v>3.85</v>
+        <v>2.91</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['83', '86']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>['14', '61', '64']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.36</v>
+        <v>3.45</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.64</v>
+        <v>1.19</v>
       </c>
       <c r="AS4" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="AT4" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46219.5</v>
@@ -1500,23 +1500,23 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '45+5', '89']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
@@ -1599,28 +1599,28 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46219.77083333334</v>
@@ -1647,139 +1647,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O8" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC8" t="n">
         <v>3.25</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '90+5']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46219.8125</v>
@@ -1806,16 +1806,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1827,118 +1827,118 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="P9" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T9" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46219.8125</v>
@@ -1974,48 +1974,48 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>4.09</v>
+        <v>3.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
         <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
         <v>2.65</v>
@@ -2024,25 +2024,25 @@
         <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD10" t="n">
         <v>1.26</v>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34', '83']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
@@ -2076,28 +2076,28 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46219.83333333334</v>
@@ -2152,68 +2152,68 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="O11" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>8.5</v>
+        <v>7.99</v>
       </c>
       <c r="Q11" t="n">
         <v>1.67</v>
       </c>
       <c r="R11" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="S11" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
         <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2315,16 +2315,16 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="O12" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
         <v>2.35</v>
@@ -2333,10 +2333,10 @@
         <v>1.29</v>
       </c>
       <c r="T12" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V12" t="n">
         <v>1.55</v>
@@ -2351,7 +2351,7 @@
         <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA12" t="n">
         <v>1.62</v>
@@ -2369,10 +2369,10 @@
         <v>1.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="O13" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T13" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
         <v>3.25</v>
@@ -2504,22 +2504,22 @@
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
         <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AB13" t="n">
         <v>1.46</v>
       </c>
       <c r="AC13" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AD13" t="n">
         <v>1.2</v>
@@ -2528,7 +2528,7 @@
         <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
         <v>1.6</v>
@@ -2629,35 +2629,35 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="O14" t="n">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="R14" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W14" t="n">
         <v>1.15</v>
@@ -2669,19 +2669,19 @@
         <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA14" t="n">
         <v>1.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE14" t="n">
         <v>1.25</v>
@@ -2706,7 +2706,7 @@
         <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2795,19 +2795,19 @@
         <v>1.44</v>
       </c>
       <c r="O15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P15" t="n">
-        <v>4.7</v>
+        <v>6.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R15" t="n">
         <v>2.7</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T15" t="n">
         <v>4.33</v>
@@ -2825,25 +2825,25 @@
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AF15" t="n">
         <v>1.5</v>
@@ -2865,7 +2865,7 @@
         <v>1.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O16" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="P16" t="n">
         <v>4.8</v>
       </c>
-      <c r="P16" t="n">
-        <v>5.1</v>
-      </c>
       <c r="Q16" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="R16" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S16" t="n">
         <v>1.2</v>
@@ -2972,10 +2972,10 @@
         <v>4.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="V16" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="W16" t="n">
         <v>1.19</v>
@@ -2984,19 +2984,19 @@
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z16" t="n">
         <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AD16" t="n">
         <v>1.75</v>
@@ -3005,10 +3005,10 @@
         <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
